--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_139_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_139_R14.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8097</v>
+        <v>5.4735</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7034</v>
+        <v>4.1319</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1063</v>
+        <v>1.3415</v>
       </c>
       <c r="G2" t="n">
         <v>1.5084</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.771</v>
+        <v>-0.1072</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0376</v>
+        <v>-0.6091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2667</v>
+        <v>0.5019</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3107</v>
+        <v>2.9838</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8156</v>
+        <v>0.4167</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.505</v>
+        <v>2.5671</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3831</v>
+        <v>0.5191</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.106</v>
+        <v>-0.0431</v>
       </c>
       <c r="I3" t="n">
-        <v>1.489</v>
+        <v>0.5622</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8526</v>
+        <v>2.2953</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3031</v>
+        <v>0.7261</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5495</v>
+        <v>1.5692</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4695</v>
+        <v>-1.7761</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4091</v>
+        <v>-0.7692</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0604</v>
+        <v>-1.0069</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>3.9432</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9796</v>
+        <v>-0.7852</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3927</v>
+        <v>-0.3967</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5869</v>
+        <v>-0.3886</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8197</v>
+        <v>0.9304</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8197</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8989</v>
+        <v>2.4451</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3657</v>
+        <v>2.8156</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2646</v>
+        <v>-0.3705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5191</v>
+        <v>0.3831</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0431</v>
+        <v>-1.106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5622</v>
+        <v>1.489</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2953</v>
+        <v>2.8526</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7261</v>
+        <v>0.3031</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5692</v>
+        <v>2.5495</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7761</v>
+        <v>-2.4695</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7692</v>
+        <v>-1.4091</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0069</v>
+        <v>-1.0604</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9432</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8701</v>
+        <v>-0.8452</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1791</v>
+        <v>-0.3927</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.4525</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>0.8197</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>0.8197</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8087</v>
+        <v>0.9603</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0328</v>
+        <v>1.0664</v>
       </c>
       <c r="G5" t="n">
         <v>0.9436</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5988</v>
+        <v>-0.4472</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6067</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2546</v>
+        <v>-0.9445</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.0484</v>
+        <v>-3.4022</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7937</v>
+        <v>2.4577</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5403</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1439</v>
+        <v>0.454</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>-0.2396</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0297</v>
+        <v>0.6937</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4046</v>
+        <v>-1.3394</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8315</v>
+        <v>-2.2286</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4269</v>
+        <v>0.8892</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1535</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3003</v>
+        <v>0.3655</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1889</v>
+        <v>-0.2082</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1114</v>
+        <v>0.5737</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.733</v>
+        <v>-1.6486</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5048</v>
+        <v>-2.3868</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7718</v>
+        <v>0.7382</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0919</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.105</v>
+        <v>-0.0206</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1111</v>
+        <v>0.0775</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9915</v>
+        <v>-1.8984</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3002</v>
+        <v>-2.6357</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3086</v>
+        <v>0.7373</v>
       </c>
       <c r="G9" t="n">
         <v>-2.073</v>
@@ -1156,13 +1156,13 @@
         <v>4.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9159</v>
+        <v>-0.8228</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.8591</v>
+        <v>-1.1947</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9432</v>
+        <v>0.3719</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3943</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8679</v>
+        <v>-4.8184</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5854</v>
+        <v>-4.8043</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2825</v>
+        <v>-0.0141</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4664</v>
+        <v>-1.0851</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6266</v>
+        <v>1.3742</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8397</v>
+        <v>-2.4593</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6436</v>
+        <v>0.6624</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7541</v>
+        <v>2.165</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1104</v>
+        <v>-1.5026</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8227</v>
+        <v>-1.7475</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8726</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.9567</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0876</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7112</v>
+        <v>-4.871</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>3.2473</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7582</v>
+        <v>-1.5736</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7695</v>
+        <v>-1.1319</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0113</v>
+        <v>-0.4417</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8855</v>
+        <v>-7.1489</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2329</v>
+        <v>-5.0008</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6526</v>
+        <v>-2.1481</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0851</v>
+        <v>-3.4664</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3742</v>
+        <v>-2.6266</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4593</v>
+        <v>-0.8397</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6624</v>
+        <v>-1.6436</v>
       </c>
       <c r="K11" t="n">
-        <v>2.165</v>
+        <v>-1.7541</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5026</v>
+        <v>0.1104</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7475</v>
+        <v>-1.8227</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.8726</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9567</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6237</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.871</v>
+        <v>-3.7112</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2473</v>
+        <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6406</v>
+        <v>-0.5228</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5604</v>
+        <v>0.3541</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0802</v>
+        <v>-0.8768</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.309100000000001</v>
+        <v>-5.935499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.5739</v>
+        <v>-13.2003</v>
       </c>
       <c r="F12" t="n">
-        <v>7.2646</v>
+        <v>7.264700000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-7.055999999999999</v>
@@ -1369,7 +1369,7 @@
         <v>3.3832</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2184999999999997</v>
+        <v>-0.2185000000000006</v>
       </c>
       <c r="M12" t="n">
         <v>-10.2206</v>
@@ -1390,10 +1390,10 @@
         <v>22.0356</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6786</v>
+        <v>-4.3051</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1645</v>
+        <v>-3.7911</v>
       </c>
       <c r="U12" t="n">
         <v>-0.5140000000000002</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9327</v>
+        <v>5.5737</v>
       </c>
       <c r="E13" t="n">
-        <v>7.1759</v>
+        <v>5.7604</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2432</v>
+        <v>-0.1867</v>
       </c>
       <c r="G13" t="n">
         <v>5.0998</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>3.137</v>
+        <v>1.7781</v>
       </c>
       <c r="T13" t="n">
-        <v>2.265</v>
+        <v>0.8496</v>
       </c>
       <c r="U13" t="n">
-        <v>0.872</v>
+        <v>0.9285</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1667</v>
+        <v>4.4761</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3673</v>
+        <v>1.7211</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7994</v>
+        <v>2.755</v>
       </c>
       <c r="G14" t="n">
         <v>5.2241</v>
@@ -1546,13 +1546,13 @@
         <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3822</v>
+        <v>-0.0727</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U14" t="n">
-        <v>0.514</v>
+        <v>0.4696</v>
       </c>
       <c r="V14" t="n">
         <v>0.2525</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.724</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3802</v>
+        <v>-0.857</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2527</v>
+        <v>2.5811</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2877</v>
+        <v>1.1464</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4081</v>
+        <v>0.6915</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1205</v>
+        <v>0.4548</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1052</v>
+        <v>1.5968</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0181</v>
+        <v>0.9782</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0871</v>
+        <v>0.6186</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1825</v>
+        <v>-0.4504</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.39</v>
+        <v>-0.2866</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2075</v>
+        <v>-0.1638</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1889</v>
+        <v>-0.0468</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1885</v>
+        <v>0.8538</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5361</v>
+        <v>0.9304</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4607</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7951</v>
+        <v>-0.6161</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3344</v>
+        <v>1.5108</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1303</v>
+        <v>-1.2877</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1069</v>
+        <v>-1.4081</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0235</v>
+        <v>0.1205</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5236</v>
+        <v>-1.1052</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3396</v>
+        <v>-1.0181</v>
       </c>
       <c r="L16" t="n">
-        <v>0.184</v>
+        <v>-0.0871</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3933</v>
+        <v>-0.1825</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2327</v>
+        <v>-0.39</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1605</v>
+        <v>0.2075</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.083</v>
+        <v>0.0226</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2715</v>
+        <v>-0.047</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1885</v>
+        <v>0.0696</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4387</v>
+        <v>0.6214</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6827</v>
+        <v>-1.83</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1213</v>
+        <v>2.4514</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1464</v>
+        <v>0.2981</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6915</v>
+        <v>0.4119</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4548</v>
+        <v>-0.1138</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5968</v>
+        <v>0.788</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9782</v>
+        <v>1.1595</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6186</v>
+        <v>-0.3716</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4504</v>
+        <v>-0.4899</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2866</v>
+        <v>-0.7477</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1638</v>
+        <v>0.2578</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4784</v>
+        <v>0.5553</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.2985</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3941</v>
+        <v>0.8538</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.244</v>
+        <v>0.6008</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4198</v>
+        <v>0.6771</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6638</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2981</v>
+        <v>0.1303</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4119</v>
+        <v>0.1069</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1138</v>
+        <v>0.0235</v>
       </c>
       <c r="J18" t="n">
-        <v>0.788</v>
+        <v>0.5236</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1595</v>
+        <v>0.3396</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3716</v>
+        <v>0.184</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4899</v>
+        <v>-0.3933</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7477</v>
+        <v>-0.2327</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2578</v>
+        <v>-0.1605</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1779</v>
+        <v>0.2232</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8883</v>
+        <v>0.1535</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0662</v>
+        <v>0.0696</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.158</v>
+        <v>-0.0386</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7046</v>
+        <v>-2.0585</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8627</v>
+        <v>2.0199</v>
       </c>
       <c r="G19" t="n">
         <v>0.3949</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3145</v>
+        <v>0.118</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1968</v>
+        <v>-0.1571</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1177</v>
+        <v>0.275</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4694</v>
+        <v>-0.1508</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2501</v>
+        <v>-0.111</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2194</v>
+        <v>-0.0398</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.305</v>
+        <v>2.2693</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8092</v>
+        <v>1.0479</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1142</v>
+        <v>1.2213</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1014</v>
+        <v>2.9197</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.1665</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6391</v>
+        <v>1.7532</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2037</v>
+        <v>-0.6504</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2714</v>
+        <v>-0.1186</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4751</v>
+        <v>-0.5319</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1598</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8536</v>
+        <v>1.2757</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7275</v>
+        <v>0.4485</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1261</v>
+        <v>0.8272</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>-1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4768</v>
+        <v>-0.509</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3469</v>
+        <v>-2.139</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1299</v>
+        <v>1.63</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2693</v>
+        <v>-0.926</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0479</v>
+        <v>-3.2113</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2213</v>
+        <v>2.2853</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9197</v>
+        <v>-0.9008</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1665</v>
+        <v>-2.5068</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7532</v>
+        <v>1.606</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6504</v>
+        <v>-0.0252</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1186</v>
+        <v>-0.7045</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5319</v>
+        <v>0.6793</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9498</v>
+        <v>0.3991</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2126</v>
+        <v>-0.0784</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7372</v>
+        <v>0.4775</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8843</v>
+        <v>-0.7225</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.021</v>
+        <v>-0.6039</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1367</v>
+        <v>-0.1185</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.926</v>
+        <v>-0.305</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2113</v>
+        <v>0.8092</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2853</v>
+        <v>-1.1142</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9008</v>
+        <v>-0.1014</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5068</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1.606</v>
+        <v>-0.6391</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0252</v>
+        <v>-0.2037</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7045</v>
+        <v>0.2714</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6793</v>
+        <v>-0.4751</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0237</v>
+        <v>0.6005</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0395</v>
+        <v>0.3736</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0158</v>
+        <v>0.2269</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1336</v>
+        <v>-4.5882</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.7253</v>
+        <v>-6.1355</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5917</v>
+        <v>1.5473</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9883</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0009</v>
+        <v>0.5445</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.731</v>
+        <v>-0.1412</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7301</v>
+        <v>0.6858</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.309199999999998</v>
+        <v>7.8816</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.192299999999999</v>
+        <v>-6.1924</v>
       </c>
       <c r="F24" t="n">
-        <v>12.5014</v>
+        <v>14.0742</v>
       </c>
       <c r="G24" t="n">
-        <v>7.055899999999999</v>
+        <v>7.0559</v>
       </c>
       <c r="H24" t="n">
-        <v>2.305299999999999</v>
+        <v>2.3053</v>
       </c>
       <c r="I24" t="n">
-        <v>4.750700000000002</v>
+        <v>4.7507</v>
       </c>
       <c r="J24" t="n">
         <v>10.2204</v>
       </c>
       <c r="K24" t="n">
-        <v>5.688200000000001</v>
+        <v>5.688199999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>4.532099999999999</v>
+        <v>4.532100000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-3.1646</v>
@@ -2314,10 +2314,10 @@
         <v>-3.3833</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2185999999999998</v>
+        <v>0.2185999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.319700000000001</v>
+        <v>-2.3197</v>
       </c>
       <c r="Q24" t="n">
         <v>-22.0356</v>
@@ -2326,19 +2326,19 @@
         <v>19.716</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6784</v>
+        <v>6.251300000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5138000000000001</v>
+        <v>0.5139</v>
       </c>
       <c r="U24" t="n">
-        <v>4.1646</v>
+        <v>5.737299999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.1059</v>
+        <v>-3.105900000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>5.1085</v>
+        <v>5.108499999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-8.214399999999999</v>
